--- a/data/AttributeAutoPlan.xlsx
+++ b/data/AttributeAutoPlan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,9 +448,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -774,6 +771,40 @@
       <c r="N14" t="inlineStr">
         <is>
           <t>法系:仙攻为主</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>403</v>
+      </c>
+      <c r="E15" t="n">
+        <v>401</v>
+      </c>
+      <c r="F15" t="n">
+        <v>404</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>宝宝通用:力量为主、体质次之、敏捷补(核心线宝宝只普攻,不投灵力)</t>
         </is>
       </c>
     </row>
